--- a/Greyform/Python_Application/Greyform PBUT1a BOM Checklist 20231211.xlsx
+++ b/Greyform/Python_Application/Greyform PBUT1a BOM Checklist 20231211.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503D2847-9550-4F91-B597-0181EFA3C5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCB9F9D-B6C0-478C-BB35-E0EF2DEDAA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{772136AB-A2BE-418F-B11F-C51AB39A70A3}"/>
+    <workbookView xWindow="2730" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{772136AB-A2BE-418F-B11F-C51AB39A70A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId1"/>

--- a/Greyform/Python_Application/Greyform PBUT1a BOM Checklist 20231211.xlsx
+++ b/Greyform/Python_Application/Greyform PBUT1a BOM Checklist 20231211.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\greyform GUI BIM Implementation\Basic GUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCB9F9D-B6C0-478C-BB35-E0EF2DEDAA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B209A6A1-7A6A-42D4-8017-813C78E39CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{772136AB-A2BE-418F-B11F-C51AB39A70A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{772136AB-A2BE-418F-B11F-C51AB39A70A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>ExpressID</t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>Remarks</t>
+  </si>
+  <si>
+    <t>BSS.10 Glass</t>
+  </si>
+  <si>
+    <t>BSS.TECE.CONCEALED CISTERN.9370224</t>
+  </si>
+  <si>
+    <t>BSS.TECE.CHAIR BRACKET.9370228</t>
+  </si>
+  <si>
+    <t>BSS.Domestic Cold Water Pipe (PPR) - WC</t>
+  </si>
+  <si>
+    <t>BSS.Domestic Cold Water Pipe (PPR) - Bib Tap</t>
+  </si>
+  <si>
+    <t>BSS.Domestic Cold Water Pipe (PPR) - Basin</t>
+  </si>
+  <si>
+    <t>BSS.Domestic Hot Water Pipe (PPR) - Basin</t>
   </si>
   <si>
     <t>BSS.MIRROR CABINET.C5-MASTER BATH</t>
@@ -66,10 +87,28 @@
     <t>BSS.HAND SHOWER SET.MASTER BATH</t>
   </si>
   <si>
+    <t>BSS.Domestic Mixed Water Pipe (PPR)</t>
+  </si>
+  <si>
+    <t>Shower Ledge</t>
+  </si>
+  <si>
+    <t>BSS.Domestic Hot Water Pipe (PPR) - Shower</t>
+  </si>
+  <si>
+    <t>BSS.Domestic Cold Water Pipe (PPR) - Shower</t>
+  </si>
+  <si>
     <t>BSS.FLOOR DRAIN_150</t>
   </si>
   <si>
     <t>BSS.FLOOR DRAIN_100</t>
+  </si>
+  <si>
+    <t>BSS.GESSI.SH.63352</t>
+  </si>
+  <si>
+    <t>2DKh1tTK5AReNfdPF8Ydwi</t>
   </si>
   <si>
     <t>2DKh1tTK5AReNfdPF8YdwV</t>
@@ -79,6 +118,18 @@
   </si>
   <si>
     <t>2DKh1tTK5AReNfdPF8YdyR</t>
+  </si>
+  <si>
+    <t>0Jl$NMCXXFov_jmC_H$9GN</t>
+  </si>
+  <si>
+    <t>3p0PZsWGP3zgFQe4OJOQNI</t>
+  </si>
+  <si>
+    <t>2bBYaMJof5HOHz4IK0w7Pn</t>
+  </si>
+  <si>
+    <t>2bBYaMJof5HOHz4IK0w7Pp</t>
   </si>
   <si>
     <t>2DKh1tTK5AReNfdPF8YdxL</t>
@@ -99,10 +150,25 @@
     <t>2DKh1tTK5AReNfdPF8Ydyc</t>
   </si>
   <si>
+    <t>2DKh1tTK5AReNfdPF8YdyS</t>
+  </si>
+  <si>
     <t>2DKh1tTK5AReNfdPF8Ydxr</t>
   </si>
   <si>
     <t>2DKh1tTK5AReNfdPF8Ydy8</t>
+  </si>
+  <si>
+    <t>2DKh1tTK5AReNfdPF8YdwG</t>
+  </si>
+  <si>
+    <t>2RzWjncHf0ifqUPE6mpFpY</t>
+  </si>
+  <si>
+    <t>1w_MMcLonBywW_fZrFACuJ</t>
+  </si>
+  <si>
+    <t>1w_MMcLonBywW_fZrFACw8</t>
   </si>
   <si>
     <t>Model: PBU_T1a</t>
@@ -111,16 +177,28 @@
     <t xml:space="preserve">Center point </t>
   </si>
   <si>
+    <t>Pipe location on wall</t>
+  </si>
+  <si>
     <t>Center point &amp; level</t>
   </si>
   <si>
-    <t>BSS.GOMGO.TR.GG</t>
+    <t>on ceiling</t>
   </si>
   <si>
-    <t>BSS.TECE.CONCEALED CISTERN</t>
+    <t>BSS.20mm Wall Finishes (600x600mm)</t>
   </si>
   <si>
-    <t>BSS.TECE.CHAIR BRACKET</t>
+    <t>Tile setting out for each wall</t>
+  </si>
+  <si>
+    <t>BSS.20mm Floor Finishes (600x600mm)</t>
+  </si>
+  <si>
+    <t>Floor tile setting out</t>
+  </si>
+  <si>
+    <t>BSS.GOMGO.TR.GG-6108-600</t>
   </si>
 </sst>
 </file>
@@ -659,92 +737,6 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>133350</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2051" name="Check Box 3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2051"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>2</xdr:row>
           <xdr:rowOff>180975</xdr:rowOff>
         </xdr:from>
         <xdr:to>
@@ -755,13 +747,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2052" name="Check Box 4" hidden="1">
+            <xdr:cNvPr id="2051" name="Check Box 3" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2052"/>
+                  <a14:compatExt spid="_x0000_s2051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -841,13 +833,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2053" name="Check Box 5" hidden="1">
+            <xdr:cNvPr id="2052" name="Check Box 4" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2053"/>
+                  <a14:compatExt spid="_x0000_s2052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -927,357 +919,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2054" name="Check Box 6" hidden="1">
+            <xdr:cNvPr id="2053" name="Check Box 5" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2054"/>
+                  <a14:compatExt spid="_x0000_s2053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2055" name="Check Box 7" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2055"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2056" name="Check Box 8" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2056"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2057" name="Check Box 9" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2057"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2058" name="Check Box 10" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2058"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1357,13 +1005,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2059" name="Check Box 11" hidden="1">
+            <xdr:cNvPr id="2054" name="Check Box 6" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2059"/>
+                  <a14:compatExt spid="_x0000_s2054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1443,13 +1091,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2060" name="Check Box 12" hidden="1">
+            <xdr:cNvPr id="2055" name="Check Box 7" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2060"/>
+                  <a14:compatExt spid="_x0000_s2055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1529,13 +1177,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2061" name="Check Box 13" hidden="1">
+            <xdr:cNvPr id="2056" name="Check Box 8" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2061"/>
+                  <a14:compatExt spid="_x0000_s2056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1615,13 +1263,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2062" name="Check Box 14" hidden="1">
+            <xdr:cNvPr id="2057" name="Check Box 9" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2062"/>
+                  <a14:compatExt spid="_x0000_s2057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1701,13 +1349,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2063" name="Check Box 15" hidden="1">
+            <xdr:cNvPr id="2058" name="Check Box 10" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2063"/>
+                  <a14:compatExt spid="_x0000_s2058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1777,23 +1425,23 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>133350</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2064" name="Check Box 16" hidden="1">
+            <xdr:cNvPr id="2059" name="Check Box 11" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2064"/>
+                  <a14:compatExt spid="_x0000_s2059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1862,24 +1510,24 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2065" name="Check Box 17" hidden="1">
+            <xdr:cNvPr id="2060" name="Check Box 12" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2065"/>
+                  <a14:compatExt spid="_x0000_s2060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1946,26 +1594,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2066" name="Check Box 18" hidden="1">
+            <xdr:cNvPr id="2061" name="Check Box 13" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2066"/>
+                  <a14:compatExt spid="_x0000_s2061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2018,7 +1666,351 @@
                   <a:latin typeface="Segoe UI"/>
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
-                <a:t>NO</a:t>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2062" name="Check Box 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2062"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2063" name="Check Box 15" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2064" name="Check Box 16" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2065" name="Check Box 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -2045,13 +2037,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2067" name="Check Box 19" hidden="1">
+            <xdr:cNvPr id="2066" name="Check Box 18" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2067"/>
+                  <a14:compatExt spid="_x0000_s2066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2131,13 +2123,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2068" name="Check Box 20" hidden="1">
+            <xdr:cNvPr id="2067" name="Check Box 19" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2068"/>
+                  <a14:compatExt spid="_x0000_s2067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2217,357 +2209,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2069" name="Check Box 21" hidden="1">
+            <xdr:cNvPr id="2068" name="Check Box 20" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2069"/>
+                  <a14:compatExt spid="_x0000_s2068"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2070" name="Check Box 22" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2070"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2071" name="Check Box 23" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2071"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2072" name="Check Box 24" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2072"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2073" name="Check Box 25" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2647,13 +2295,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2074" name="Check Box 26" hidden="1">
+            <xdr:cNvPr id="2069" name="Check Box 21" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2074"/>
+                  <a14:compatExt spid="_x0000_s2069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2733,13 +2381,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2075" name="Check Box 27" hidden="1">
+            <xdr:cNvPr id="2070" name="Check Box 22" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2075"/>
+                  <a14:compatExt spid="_x0000_s2070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2819,13 +2467,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2076" name="Check Box 28" hidden="1">
+            <xdr:cNvPr id="2071" name="Check Box 23" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2076"/>
+                  <a14:compatExt spid="_x0000_s2071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2905,13 +2553,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2077" name="Check Box 29" hidden="1">
+            <xdr:cNvPr id="2072" name="Check Box 24" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2077"/>
+                  <a14:compatExt spid="_x0000_s2072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2991,13 +2639,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2078" name="Check Box 30" hidden="1">
+            <xdr:cNvPr id="2073" name="Check Box 25" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2078"/>
+                  <a14:compatExt spid="_x0000_s2073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3051,608 +2699,6 @@
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2079" name="Check Box 31" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2080" name="Check Box 32" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2081" name="Check Box 33" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2082" name="Check Box 34" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2083" name="Check Box 35" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2084" name="Check Box 36" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2085" name="Check Box 37" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -3679,13 +2725,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2086" name="Check Box 38" hidden="1">
+            <xdr:cNvPr id="2074" name="Check Box 26" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2086"/>
+                  <a14:compatExt spid="_x0000_s2074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3739,92 +2785,6 @@
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2087" name="Check Box 39" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2087"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -3851,13 +2811,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2088" name="Check Box 40" hidden="1">
+            <xdr:cNvPr id="2075" name="Check Box 27" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2088"/>
+                  <a14:compatExt spid="_x0000_s2075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3911,608 +2871,6 @@
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2089" name="Check Box 41" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2089"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2090" name="Check Box 42" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2090"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2091" name="Check Box 43" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2091"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2092" name="Check Box 44" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2092"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2093" name="Check Box 45" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>152400</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2094" name="Check Box 46" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2095" name="Check Box 47" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2095"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -4539,13 +2897,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2096" name="Check Box 48" hidden="1">
+            <xdr:cNvPr id="2076" name="Check Box 28" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2096"/>
+                  <a14:compatExt spid="_x0000_s2076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4599,92 +2957,6 @@
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2097" name="Check Box 49" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -4711,13 +2983,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2098" name="Check Box 50" hidden="1">
+            <xdr:cNvPr id="2077" name="Check Box 29" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2098"/>
+                  <a14:compatExt spid="_x0000_s2077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4771,92 +3043,6 @@
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2099" name="Check Box 51" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -4883,13 +3069,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2100" name="Check Box 52" hidden="1">
+            <xdr:cNvPr id="2078" name="Check Box 30" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2100"/>
+                  <a14:compatExt spid="_x0000_s2078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4943,92 +3129,6 @@
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2101" name="Check Box 53" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -5055,13 +3155,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2102" name="Check Box 54" hidden="1">
+            <xdr:cNvPr id="2079" name="Check Box 31" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2102"/>
+                  <a14:compatExt spid="_x0000_s2079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5115,92 +3215,6 @@
                   <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>NO</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>438150</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2103" name="Check Box 55" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2103"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>YES</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -5223,6 +3237,2070 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>457200</xdr:colOff>
           <xdr:row>18</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2080" name="Check Box 32" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2081" name="Check Box 33" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2082" name="Check Box 34" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2083" name="Check Box 35" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2084" name="Check Box 36" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2084"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2085" name="Check Box 37" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2085"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2086" name="Check Box 38" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2086"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2087" name="Check Box 39" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2087"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2088" name="Check Box 40" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2088"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2089" name="Check Box 41" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2089"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2090" name="Check Box 42" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2090"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2091" name="Check Box 43" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2092" name="Check Box 44" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2093" name="Check Box 45" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2094" name="Check Box 46" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2095" name="Check Box 47" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2095"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2096" name="Check Box 48" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2096"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2097" name="Check Box 49" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2097"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2098" name="Check Box 50" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2098"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2099" name="Check Box 51" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2099"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2100" name="Check Box 52" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2100"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2101" name="Check Box 53" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2101"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2102" name="Check Box 54" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2102"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>NO</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>438150</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2103" name="Check Box 55" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2103"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-SG" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>YES</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>152400</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5596,7 +5674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA961391-8557-48B9-B65D-C17244EABD99}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
@@ -5610,7 +5688,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5621,7 +5699,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -5642,16 +5720,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>277533</v>
+        <v>278743</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -5659,143 +5737,147 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>101982</v>
+        <v>277533</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>86686</v>
+        <v>101982</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>179973</v>
+        <v>86686</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>179630</v>
+        <v>22100</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>278665</v>
+        <v>32074</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>243877</v>
+        <v>21681</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>169935</v>
+        <v>21598</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
-        <v>183181</v>
+        <v>179973</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -5803,16 +5885,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>77151</v>
+        <v>179630</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -5820,69 +5902,281 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>278665</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>24</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>243877</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>25</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>169935</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>26</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>32646</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>27</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>77210</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>28</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>23322</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>29389</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>183181</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>77151</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>275881</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5891,15 +6185,14 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2049" r:id="rId4" name="Check Box 1">
+            <control shapeId="2049" r:id="rId3" name="Check Box 1">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5921,7 +6214,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2050" r:id="rId5" name="Check Box 2">
+            <control shapeId="2050" r:id="rId4" name="Check Box 2">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5943,29 +6236,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2051" r:id="rId6" name="Check Box 3">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>2</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>3</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2052" r:id="rId7" name="Check Box 4">
+            <control shapeId="2051" r:id="rId5" name="Check Box 3">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5987,7 +6258,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2053" r:id="rId8" name="Check Box 5">
+            <control shapeId="2052" r:id="rId6" name="Check Box 4">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6009,7 +6280,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2054" r:id="rId9" name="Check Box 6">
+            <control shapeId="2053" r:id="rId7" name="Check Box 5">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6031,95 +6302,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2055" r:id="rId10" name="Check Box 7">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2056" r:id="rId11" name="Check Box 8">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2057" r:id="rId12" name="Check Box 9">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2058" r:id="rId13" name="Check Box 10">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2059" r:id="rId14" name="Check Box 11">
+            <control shapeId="2054" r:id="rId8" name="Check Box 6">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6141,7 +6324,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2060" r:id="rId15" name="Check Box 12">
+            <control shapeId="2055" r:id="rId9" name="Check Box 7">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6163,7 +6346,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2061" r:id="rId16" name="Check Box 13">
+            <control shapeId="2056" r:id="rId10" name="Check Box 8">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6185,7 +6368,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2062" r:id="rId17" name="Check Box 14">
+            <control shapeId="2057" r:id="rId11" name="Check Box 9">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6207,7 +6390,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2063" r:id="rId18" name="Check Box 15">
+            <control shapeId="2058" r:id="rId12" name="Check Box 10">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6229,20 +6412,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2064" r:id="rId19" name="Check Box 16">
+            <control shapeId="2059" r:id="rId13" name="Check Box 11">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>133350</xdr:colOff>
                     <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
+                    <xdr:rowOff>180975</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6251,20 +6434,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2065" r:id="rId20" name="Check Box 17">
+            <control shapeId="2060" r:id="rId14" name="Check Box 12">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6273,20 +6456,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2066" r:id="rId21" name="Check Box 18">
+            <control shapeId="2061" r:id="rId15" name="Check Box 13">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>2</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>3</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6295,7 +6478,95 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2067" r:id="rId22" name="Check Box 19">
+            <control shapeId="2062" r:id="rId16" name="Check Box 14">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2063" r:id="rId17" name="Check Box 15">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2064" r:id="rId18" name="Check Box 16">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2065" r:id="rId19" name="Check Box 17">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2066" r:id="rId20" name="Check Box 18">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6317,7 +6588,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2068" r:id="rId23" name="Check Box 20">
+            <control shapeId="2067" r:id="rId21" name="Check Box 19">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6339,7 +6610,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2069" r:id="rId24" name="Check Box 21">
+            <control shapeId="2068" r:id="rId22" name="Check Box 20">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6361,95 +6632,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2070" r:id="rId25" name="Check Box 22">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2071" r:id="rId26" name="Check Box 23">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2072" r:id="rId27" name="Check Box 24">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2073" r:id="rId28" name="Check Box 25">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2074" r:id="rId29" name="Check Box 26">
+            <control shapeId="2069" r:id="rId23" name="Check Box 21">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6471,7 +6654,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2075" r:id="rId30" name="Check Box 27">
+            <control shapeId="2070" r:id="rId24" name="Check Box 22">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6493,7 +6676,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2076" r:id="rId31" name="Check Box 28">
+            <control shapeId="2071" r:id="rId25" name="Check Box 23">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6515,7 +6698,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2077" r:id="rId32" name="Check Box 29">
+            <control shapeId="2072" r:id="rId26" name="Check Box 24">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6537,7 +6720,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2078" r:id="rId33" name="Check Box 30">
+            <control shapeId="2073" r:id="rId27" name="Check Box 25">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6559,161 +6742,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2079" r:id="rId34" name="Check Box 31">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2080" r:id="rId35" name="Check Box 32">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2081" r:id="rId36" name="Check Box 33">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2082" r:id="rId37" name="Check Box 34">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2083" r:id="rId38" name="Check Box 35">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2084" r:id="rId39" name="Check Box 36">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2085" r:id="rId40" name="Check Box 37">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2086" r:id="rId41" name="Check Box 38">
+            <control shapeId="2074" r:id="rId28" name="Check Box 26">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6735,29 +6764,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2087" r:id="rId42" name="Check Box 39">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2088" r:id="rId43" name="Check Box 40">
+            <control shapeId="2075" r:id="rId29" name="Check Box 27">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6779,161 +6786,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2089" r:id="rId44" name="Check Box 41">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2090" r:id="rId45" name="Check Box 42">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2091" r:id="rId46" name="Check Box 43">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2092" r:id="rId47" name="Check Box 44">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2093" r:id="rId48" name="Check Box 45">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2094" r:id="rId49" name="Check Box 46">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>152400</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>457200</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>28575</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2095" r:id="rId50" name="Check Box 47">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2096" r:id="rId51" name="Check Box 48">
+            <control shapeId="2076" r:id="rId30" name="Check Box 28">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6955,29 +6808,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2097" r:id="rId52" name="Check Box 49">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2098" r:id="rId53" name="Check Box 50">
+            <control shapeId="2077" r:id="rId31" name="Check Box 29">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6999,29 +6830,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2099" r:id="rId54" name="Check Box 51">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2100" r:id="rId55" name="Check Box 52">
+            <control shapeId="2078" r:id="rId32" name="Check Box 30">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7043,29 +6852,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2101" r:id="rId56" name="Check Box 53">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>17</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2102" r:id="rId57" name="Check Box 54">
+            <control shapeId="2079" r:id="rId33" name="Check Box 31">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7087,29 +6874,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2103" r:id="rId58" name="Check Box 55">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>438150</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="2104" r:id="rId59" name="Check Box 56">
+            <control shapeId="2080" r:id="rId34" name="Check Box 32">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7129,6 +6894,534 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2081" r:id="rId35" name="Check Box 33">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2082" r:id="rId36" name="Check Box 34">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2083" r:id="rId37" name="Check Box 35">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2084" r:id="rId38" name="Check Box 36">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2085" r:id="rId39" name="Check Box 37">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2086" r:id="rId40" name="Check Box 38">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2087" r:id="rId41" name="Check Box 39">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2088" r:id="rId42" name="Check Box 40">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2089" r:id="rId43" name="Check Box 41">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2090" r:id="rId44" name="Check Box 42">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2091" r:id="rId45" name="Check Box 43">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2092" r:id="rId46" name="Check Box 44">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2093" r:id="rId47" name="Check Box 45">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2094" r:id="rId48" name="Check Box 46">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2095" r:id="rId49" name="Check Box 47">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2096" r:id="rId50" name="Check Box 48">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2097" r:id="rId51" name="Check Box 49">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2098" r:id="rId52" name="Check Box 50">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2099" r:id="rId53" name="Check Box 51">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2100" r:id="rId54" name="Check Box 52">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2101" r:id="rId55" name="Check Box 53">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2102" r:id="rId56" name="Check Box 54">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2103" r:id="rId57" name="Check Box 55">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>133350</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>438150</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2104" r:id="rId58" name="Check Box 56">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>152400</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>457200</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>
